--- a/resources/hero/hero.xlsx
+++ b/resources/hero/hero.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hero" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hero" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">Hero!#REF!</definedName>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G6" s="19" t="n"/>
       <c r="H6" s="19" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="K6" s="19" t="n">
-        <v>6666</v>
+        <v>5800</v>
       </c>
       <c r="L6" s="19" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="N6" s="19" t="n">
-        <v>100</v>
+        <v>3500</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>100</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G7" s="19" t="n"/>
       <c r="H7" s="19" t="n">
-        <v>1000</v>
+        <v>13500</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>1000</v>
@@ -1364,10 +1364,10 @@
         <v>1000</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>1000</v>
+        <v>5500</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>10</v>
+        <v>3700</v>
       </c>
       <c r="N7" s="19" t="n">
         <v>100</v>

--- a/resources/hero/hero.xlsx
+++ b/resources/hero/hero.xlsx
@@ -901,7 +901,7 @@
           <t>生成文件</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -919,7 +919,7 @@
       <c r="E4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="G6" s="19" t="n"/>
       <c r="H6" s="19" t="n">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="I6" s="19" t="n">
         <v>1000</v>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="K6" s="19" t="n">
-        <v>5800</v>
+        <v>1000</v>
       </c>
       <c r="L6" s="19" t="n">
         <v>1000</v>
@@ -1309,7 +1309,7 @@
         <v>10</v>
       </c>
       <c r="N6" s="19" t="n">
-        <v>3500</v>
+        <v>100</v>
       </c>
       <c r="O6" s="19" t="n">
         <v>100</v>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="G7" s="19" t="n"/>
       <c r="H7" s="19" t="n">
-        <v>13500</v>
+        <v>1000</v>
       </c>
       <c r="I7" s="19" t="n">
         <v>1000</v>
@@ -1364,10 +1364,10 @@
         <v>1000</v>
       </c>
       <c r="L7" s="19" t="n">
-        <v>5500</v>
+        <v>1000</v>
       </c>
       <c r="M7" s="19" t="n">
-        <v>3700</v>
+        <v>10</v>
       </c>
       <c r="N7" s="19" t="n">
         <v>100</v>
